--- a/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Event Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Manager" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Event Manager'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +81,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -143,54 +150,65 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -550,15 +568,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -566,6 +585,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -594,9 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -618,8 +636,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -628,18 +663,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -852,6 +888,7 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
@@ -1067,6 +1104,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -1263,6 +1301,7 @@
       <c r="F36" s="11" t="n"/>
       <c r="G36" s="13" t="n"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
@@ -1439,6 +1478,26 @@
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="11" t="n"/>
       <c r="G46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C47">
+        <f>COUNTIF(E6:E46,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E47">
+        <f>COUNTIF(B6:B46,"?*")</f>
+        <v>35.0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -1465,11 +1524,25 @@
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A38:G38"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G46">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32 E33 E34 E35 E36 E40 E41 E42 E43 E44 E45 E46" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32 E33 E34 E35 E36 E40 E41 E42 E43 E44 E45 E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Manager" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Event Manager'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Trimestral y Anual'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -88,7 +90,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +127,16 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -152,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,6 +206,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -570,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -638,9 +656,45 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Más allá del evento:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge lo que se CONTRATA y se pide por escrito en una inspección: DDD de la cocina central, conductos de extracción, extintores, instalación de gas, certificado ATP del vehículo, calibración de sondas, aceite usado, RGSEAA, carnés de manipulador, póliza de eventos y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ Anota en «Notas» el número de parte de cada revisión y la fecha de la siguiente; la columna «Cadencia» ya viene con la periodicidad legal o recomendada de cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ En el post-evento se cierra y se valida el registro de jornada de todo el equipo, extras incluidos: montaje y desmontaje también son horas y hay que conservarlas 4 años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -665,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1466,7 +1520,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Actualizar P&amp;L del evento: costes reales vs. presupuestado</t>
+          <t>Cerrar y validar el registro de jornada de todo el equipo del evento, extras incluidos (montaje, servicio y desmontaje), y archivarlo con el del mes: hay que conservarlo 4 años</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -1480,34 +1534,53 @@
       <c r="G46" s="13" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="18" t="inlineStr">
+      <c r="A47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Actualizar P&amp;L del evento: costes reales vs. presupuestado</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="G47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C47">
-        <f>COUNTIF(E6:E46,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48">
+        <f>COUNTIFS(B6:B47,"?*",E6:E47,"✓")-COUNTIFS(B6:B47,"Tarea",E6:E47,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E47">
-        <f>COUNTIF(B6:B46,"?*")</f>
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E48">
+        <f>COUNTIF(B6:B47,"?*")-COUNTIF(B6:B47,"Tarea")-COUNTIF(E6:E47,"N/A")</f>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1516,22 +1589,776 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G46">
+  <conditionalFormatting sqref="A6:G47">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32 E33 E34 E35 E36 E40 E41 E42 E43 E44 E45 E46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E17 E18 E19 E20 E21 E22 E23 E24 E25 E29 E30 E31 E32 E33 E34 E35 E36 E40 E41 E42 E43 E44 E45 E46 E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF8E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit de Tareas: Catering / Eventos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Higiene y plagas — empresa autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD) de la cocina central: visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza de campana y conductos de extracción por empresa homologada, con certificado</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Analítica de superficies y de producto en laboratorio externo (verificación del plan de higiene)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Revisar el plan APPCC y las fichas de proveedor: altas, bajas y cambios de menú del año</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Renovar los carnés de manipulador de alimentos del equipo fijo y archivar los de los extras habituales</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que el registro sanitario (RGSEAA) recoge la actividad de catering y las cocinas que usas</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Vehículos y cadena de frío</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Renovar el certificado de conformidad ATP del vehículo isotermo o frigorífico</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del equipo de frío del vehículo por frigorista: gas, estanqueidad y termógrafo</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Calibrar termómetros y sondas contra un patrón conocido (agua con hielo, 0 °C) y anotar la desviación</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>ITV del vehículo y revisión del extintor de a bordo</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza y desinfección a fondo del vehículo con registro firmado</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Equipos, gas y residuos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Revisión periódica de la instalación de gas por empresa habilitada, si la cocina tiene gas</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de cámaras, abatidor y hornos por el SAT: juntas, sondas y consumo</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE de la cocina central por empresa mantenedora (etiqueta y acta)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Retirada del aceite usado por gestor autorizado y archivo del documento de entrega</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>Producción</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Documentación, seguros y facturación</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Revisar la póliza de responsabilidad civil de eventos: suma asegurada, aforos cubiertos y actividades excluidas</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Revisar los contratos y las altas de personal eventual del trimestre y archivar los registros de jornada</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Actualizar precios de escandallo y tarifas de evento con los precios reales de proveedor</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Anotar en «Notas» el nº de parte de cada revisión y la fecha de la siguiente</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C35">
+        <f>COUNTIFS(B6:B34,"?*",E6:E34,"✓")-COUNTIFS(B6:B34,"Tarea",E6:E34,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E35">
+        <f>COUNTIF(B6:B34,"?*")-COUNTIF(B6:B34,"Tarea")-COUNTIF(E6:E34,"N/A")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A13:G13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A6:G34">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26 E30 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/03-tareas-manager.xlsx
@@ -1589,9 +1589,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A27:G27"/>
@@ -1627,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2327,26 +2327,13 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A37:G37"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A13:G13"/>
